--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_individual_h_8.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_individual_h_8.xlsx
@@ -658,7 +658,7 @@
         <v>0.008471483344799909</v>
       </c>
       <c r="C2" t="n">
-        <v>50771040</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>50771040</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>35781434</v>
+        <v>4042820</v>
       </c>
       <c r="L2" t="n">
-        <v>19928299</v>
+        <v>1987505</v>
       </c>
       <c r="M2" t="n">
-        <v>4622220</v>
+        <v>421134</v>
       </c>
       <c r="N2" t="n">
-        <v>155521</v>
+        <v>12100</v>
       </c>
       <c r="O2" t="n">
-        <v>2721579</v>
+        <v>261498</v>
       </c>
       <c r="P2" t="n">
-        <v>1050814</v>
+        <v>105069</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999951720237732</v>
+        <v>0.9999963641166687</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8700767755508423</v>
+        <v>0.7846418619155884</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7439344525337219</v>
+        <v>0.5950733423233032</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6763379573822021</v>
+        <v>0.4929106533527374</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1985152363777161</v>
+        <v>0.1254016011953354</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7238215208053589</v>
+        <v>0.5566001534461975</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8294175863265991</v>
+        <v>0.671200156211853</v>
       </c>
       <c r="X2" t="n">
-        <v>50771040</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>50771040</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>38712019</v>
+        <v>4813274</v>
       </c>
       <c r="AG2" t="n">
-        <v>23936510</v>
+        <v>3010697</v>
       </c>
       <c r="AH2" t="n">
-        <v>6414507</v>
+        <v>804213</v>
       </c>
       <c r="AI2" t="n">
-        <v>473159</v>
+        <v>59267</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3676427</v>
+        <v>460431</v>
       </c>
       <c r="AK2" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9563227891921997</v>
+        <v>0.9555724859237671</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114070534706116</v>
+        <v>0.9118132591247559</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580120801925659</v>
+        <v>0.8582125902175903</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6619145274162292</v>
+        <v>0.6612037420272827</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019697904586792</v>
+        <v>0.9019888043403625</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314440488815308</v>
+        <v>0.9314650297164917</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002029531499543211</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>35781434</v>
+        <v>4042820</v>
       </c>
       <c r="E3" t="n">
-        <v>4530726</v>
+        <v>942935</v>
       </c>
       <c r="F3" t="n">
-        <v>100104</v>
+        <v>35714</v>
       </c>
       <c r="G3" t="n">
-        <v>8241</v>
+        <v>2592</v>
       </c>
       <c r="H3" t="n">
-        <v>6764</v>
+        <v>2784</v>
       </c>
       <c r="I3" t="n">
-        <v>362</v>
+        <v>192</v>
       </c>
       <c r="J3" t="n">
-        <v>80556716</v>
+        <v>10069597</v>
       </c>
       <c r="K3" t="n">
-        <v>85557332</v>
+        <v>10279341</v>
       </c>
       <c r="L3" t="n">
-        <v>98162449</v>
+        <v>11754065</v>
       </c>
       <c r="M3" t="n">
-        <v>121633718</v>
+        <v>15043975</v>
       </c>
       <c r="N3" t="n">
-        <v>129984607</v>
+        <v>16241836</v>
       </c>
       <c r="O3" t="n">
-        <v>126211323</v>
+        <v>15696752</v>
       </c>
       <c r="P3" t="n">
-        <v>129564762</v>
+        <v>16170940</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8850733637809753</v>
+        <v>0.8042149543762207</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7575531005859375</v>
+        <v>0.6005441546440125</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6177526712417603</v>
+        <v>0.4485985636711121</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2173620164394379</v>
+        <v>0.1347828954458237</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6673412322998047</v>
+        <v>0.5118048787117004</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6792056560516357</v>
+        <v>0.5427398085594177</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>38712019</v>
+        <v>4813274</v>
       </c>
       <c r="Z3" t="n">
-        <v>1591784</v>
+        <v>198388</v>
       </c>
       <c r="AA3" t="n">
-        <v>68580</v>
+        <v>8469</v>
       </c>
       <c r="AB3" t="n">
-        <v>54698</v>
+        <v>6867</v>
       </c>
       <c r="AC3" t="n">
-        <v>326</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>80556960</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>89132297</v>
+        <v>11165177</v>
       </c>
       <c r="AG3" t="n">
-        <v>102695121</v>
+        <v>12815311</v>
       </c>
       <c r="AH3" t="n">
-        <v>122784182</v>
+        <v>15344357</v>
       </c>
       <c r="AI3" t="n">
-        <v>130370832</v>
+        <v>16295858</v>
       </c>
       <c r="AJ3" t="n">
-        <v>126850187</v>
+        <v>15855036</v>
       </c>
       <c r="AK3" t="n">
-        <v>129674836</v>
+        <v>16209148</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575629830360413</v>
+        <v>0.9574769735336304</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099209904670715</v>
+        <v>0.9097115993499756</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8572890758514404</v>
+        <v>0.8566603064537048</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6613048911094666</v>
+        <v>0.6601800322532654</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014734625816345</v>
+        <v>0.9011573195457458</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312471747398376</v>
+        <v>0.9310656785964966</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03203123381705863</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5000390</v>
+        <v>1028950</v>
       </c>
       <c r="E4" t="n">
-        <v>19928299</v>
+        <v>1987505</v>
       </c>
       <c r="F4" t="n">
-        <v>1204542</v>
+        <v>239637</v>
       </c>
       <c r="G4" t="n">
-        <v>53972</v>
+        <v>14803</v>
       </c>
       <c r="H4" t="n">
-        <v>107980</v>
+        <v>34399</v>
       </c>
       <c r="I4" t="n">
-        <v>10954</v>
+        <v>4212</v>
       </c>
       <c r="J4" t="n">
-        <v>244</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>5343021</v>
+        <v>1109620</v>
       </c>
       <c r="L4" t="n">
-        <v>6859410</v>
+        <v>1352428</v>
       </c>
       <c r="M4" t="n">
-        <v>2211967</v>
+        <v>433248</v>
       </c>
       <c r="N4" t="n">
-        <v>627900</v>
+        <v>84390</v>
       </c>
       <c r="O4" t="n">
-        <v>1038435</v>
+        <v>208315</v>
       </c>
       <c r="P4" t="n">
-        <v>216116</v>
+        <v>51470</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999975562095642</v>
+        <v>0.999998152256012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8775110244750977</v>
+        <v>0.7943078279495239</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7506820559501648</v>
+        <v>0.5977962613105774</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6457191705703735</v>
+        <v>0.4697118401527405</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2075115740299225</v>
+        <v>0.1299231201410294</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6944348812103271</v>
+        <v>0.5332634449005127</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7468334436416626</v>
+        <v>0.6001731157302856</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1650806</v>
+        <v>208961</v>
       </c>
       <c r="Z4" t="n">
-        <v>23936510</v>
+        <v>3010697</v>
       </c>
       <c r="AA4" t="n">
-        <v>664902</v>
+        <v>83070</v>
       </c>
       <c r="AB4" t="n">
-        <v>44224</v>
+        <v>5580</v>
       </c>
       <c r="AC4" t="n">
-        <v>9155</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>544</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1768056</v>
+        <v>223784</v>
       </c>
       <c r="AG4" t="n">
-        <v>2326738</v>
+        <v>291182</v>
       </c>
       <c r="AH4" t="n">
-        <v>1061503</v>
+        <v>132866</v>
       </c>
       <c r="AI4" t="n">
-        <v>241675</v>
+        <v>30368</v>
       </c>
       <c r="AJ4" t="n">
-        <v>399571</v>
+        <v>50031</v>
       </c>
       <c r="AK4" t="n">
-        <v>106042</v>
+        <v>13262</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569424390792847</v>
+        <v>0.9565237760543823</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910663366317749</v>
+        <v>0.9107611775398254</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576504588127136</v>
+        <v>0.8574357628822327</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6616095304489136</v>
+        <v>0.660691499710083</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017215967178345</v>
+        <v>0.9015728235244751</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313456416130066</v>
+        <v>0.9312652945518494</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>236022</v>
+        <v>58989</v>
       </c>
       <c r="E5" t="n">
-        <v>1971389</v>
+        <v>325876</v>
       </c>
       <c r="F5" t="n">
-        <v>4622220</v>
+        <v>421134</v>
       </c>
       <c r="G5" t="n">
-        <v>184046</v>
+        <v>27871</v>
       </c>
       <c r="H5" t="n">
-        <v>426063</v>
+        <v>92265</v>
       </c>
       <c r="I5" t="n">
-        <v>42566</v>
+        <v>12640</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4646213</v>
+        <v>984219</v>
       </c>
       <c r="L5" t="n">
-        <v>6377842</v>
+        <v>1322002</v>
       </c>
       <c r="M5" t="n">
-        <v>2860095</v>
+        <v>517643</v>
       </c>
       <c r="N5" t="n">
-        <v>559972</v>
+        <v>77674</v>
       </c>
       <c r="O5" t="n">
-        <v>1356663</v>
+        <v>249435</v>
       </c>
       <c r="P5" t="n">
-        <v>496308</v>
+        <v>88521</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.999998152256012</v>
+        <v>0.9999985694885254</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9239367246627808</v>
+        <v>0.8724513053894043</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8992046713829041</v>
+        <v>0.8370839357376099</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9613786935806274</v>
+        <v>0.9420753717422485</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9909549355506897</v>
+        <v>0.9901276826858521</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9817624688148499</v>
+        <v>0.9721156358718872</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9945752024650574</v>
+        <v>0.9914723038673401</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>64693</v>
+        <v>8176</v>
       </c>
       <c r="Z5" t="n">
-        <v>684803</v>
+        <v>86508</v>
       </c>
       <c r="AA5" t="n">
-        <v>6414507</v>
+        <v>804213</v>
       </c>
       <c r="AB5" t="n">
-        <v>79806</v>
+        <v>10008</v>
       </c>
       <c r="AC5" t="n">
-        <v>233442</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>5064</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1715628</v>
+        <v>213765</v>
       </c>
       <c r="AG5" t="n">
-        <v>2369631</v>
+        <v>298810</v>
       </c>
       <c r="AH5" t="n">
-        <v>1067808</v>
+        <v>134564</v>
       </c>
       <c r="AI5" t="n">
-        <v>242334</v>
+        <v>30507</v>
       </c>
       <c r="AJ5" t="n">
-        <v>401815</v>
+        <v>50502</v>
       </c>
       <c r="AK5" t="n">
-        <v>106369</v>
+        <v>13345</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734734296798706</v>
+        <v>0.9733461737632751</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642394185066223</v>
+        <v>0.9640599489212036</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837862849235535</v>
+        <v>0.9837091565132141</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.996314525604248</v>
+        <v>0.9962917566299438</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938978552818298</v>
+        <v>0.9938759207725525</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998382568359375</v>
+        <v>0.9983792304992676</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>96960</v>
+        <v>16588</v>
       </c>
       <c r="E6" t="n">
-        <v>166636</v>
+        <v>23526</v>
       </c>
       <c r="F6" t="n">
-        <v>222041</v>
+        <v>24879</v>
       </c>
       <c r="G6" t="n">
-        <v>155521</v>
+        <v>12100</v>
       </c>
       <c r="H6" t="n">
-        <v>67979</v>
+        <v>11060</v>
       </c>
       <c r="I6" t="n">
-        <v>6314</v>
+        <v>1614</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>52110</v>
+        <v>6591</v>
       </c>
       <c r="Z6" t="n">
-        <v>43017</v>
+        <v>5395</v>
       </c>
       <c r="AA6" t="n">
-        <v>87434</v>
+        <v>11026</v>
       </c>
       <c r="AB6" t="n">
-        <v>473159</v>
+        <v>59267</v>
       </c>
       <c r="AC6" t="n">
-        <v>55925</v>
+        <v>7014</v>
       </c>
       <c r="AD6" t="n">
-        <v>3848</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>9362</v>
+        <v>5008</v>
       </c>
       <c r="E7" t="n">
-        <v>177430</v>
+        <v>54859</v>
       </c>
       <c r="F7" t="n">
-        <v>649679</v>
+        <v>121768</v>
       </c>
       <c r="G7" t="n">
-        <v>364263</v>
+        <v>34987</v>
       </c>
       <c r="H7" t="n">
-        <v>2721579</v>
+        <v>261498</v>
       </c>
       <c r="I7" t="n">
-        <v>155920</v>
+        <v>32812</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>223</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>6486</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>237939</v>
+        <v>29968</v>
       </c>
       <c r="AB7" t="n">
-        <v>60821</v>
+        <v>7646</v>
       </c>
       <c r="AC7" t="n">
-        <v>3676427</v>
+        <v>460431</v>
       </c>
       <c r="AD7" t="n">
-        <v>96346</v>
+        <v>12050</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>164</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>287</v>
+        <v>85</v>
       </c>
       <c r="E8" t="n">
-        <v>13229</v>
+        <v>5232</v>
       </c>
       <c r="F8" t="n">
-        <v>35601</v>
+        <v>11250</v>
       </c>
       <c r="G8" t="n">
-        <v>17378</v>
+        <v>4137</v>
       </c>
       <c r="H8" t="n">
-        <v>429649</v>
+        <v>67807</v>
       </c>
       <c r="I8" t="n">
-        <v>1050814</v>
+        <v>105069</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>648</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2648</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2126</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>100723</v>
+        <v>12636</v>
       </c>
       <c r="AD8" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
